--- a/.opencode/skills/invoice-processing/summary.xlsx
+++ b/.opencode/skills/invoice-processing/summary.xlsx
@@ -1,136 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Qing\Allgemeine\Privat\Faqiaos\202603\Private\Deductibel Faqiaos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C7B42F-3450-47BF-ADB1-A144BE1BC6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="18676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="18676" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Bills for Expat IIT deduction</t>
-  </si>
-  <si>
-    <t>Food &amp; Meals</t>
-  </si>
-  <si>
-    <t>Month:</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Handed in by:</t>
-  </si>
-  <si>
-    <t>Date &amp; Signature</t>
-  </si>
-  <si>
-    <t>Laundry</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>AMOUNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rental fee </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Qing Cheng</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Airticket </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>March of 2026</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Invoice is provided in March.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -201,50 +134,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -534,274 +526,295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="33.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.46484375" style="8" customWidth="1"/>
+    <col width="33.265625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.265625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.46484375" customWidth="1" style="8" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="14">
-        <f>89+95+151+176+191+205+241+354+359+378+400+426+463+494+576+663+682+990+460+447+2024</f>
-        <v>9864</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="68.25" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Bills for Expat IIT deduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="7" t="n"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Handed in by:</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Qing Cheng</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Month:</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Laundry</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Food &amp; Meals</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="68.25" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rental fee </t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="17"/>
-    </row>
-    <row r="18" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-    </row>
-    <row r="32" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" spans="1:4" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
-    </row>
-    <row r="35" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-    </row>
-    <row r="36" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
-    </row>
-    <row r="37" spans="1:4" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13"/>
-    </row>
-    <row r="38" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="5"/>
+      <c r="D14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airticket </t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="17" t="n"/>
+    </row>
+    <row r="18" hidden="1" ht="14.25" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="4" t="n"/>
+    </row>
+    <row r="19" hidden="1" ht="14.25" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="4" t="n"/>
+    </row>
+    <row r="20" hidden="1" ht="14.25" customHeight="1">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="4" t="n"/>
+    </row>
+    <row r="21" hidden="1" ht="14.25" customHeight="1">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22" hidden="1" ht="14.25" customHeight="1">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="4" t="n"/>
+    </row>
+    <row r="23" hidden="1" ht="14.25" customHeight="1">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24" hidden="1" ht="14.25" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25" hidden="1" ht="14.25" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="4" t="n"/>
+    </row>
+    <row r="26" hidden="1" ht="14.25" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="n"/>
+    </row>
+    <row r="27" hidden="1" ht="14.25" customHeight="1">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="4" t="n"/>
+    </row>
+    <row r="28" hidden="1" ht="14.25" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="4" t="n"/>
+    </row>
+    <row r="29" hidden="1" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30" hidden="1" ht="14.25" customHeight="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="4" t="n"/>
+    </row>
+    <row r="31" hidden="1" ht="14.25" customHeight="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="4" t="n"/>
+    </row>
+    <row r="32" hidden="1" ht="14.25" customHeight="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="4" t="n"/>
+    </row>
+    <row r="33" hidden="1" ht="14.25" customHeight="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="4" t="n"/>
+    </row>
+    <row r="34" hidden="1" ht="14.25" customHeight="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="13" t="n"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
       <c r="C38" s="15">
         <f>SUM(C10:C37)</f>
-        <v>39864</v>
-      </c>
-      <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="1:4" ht="13.9" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>5</v>
+        <v/>
+      </c>
+      <c r="D38" s="8" t="n"/>
+    </row>
+    <row r="39" ht="13.9" customHeight="1" thickTop="1"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Date &amp; Signature</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B12:C26">
-    <sortCondition ref="B12"/>
-  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="1.6666666666666667" right="0.7" top="1.15625" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="1.666666666666667" right="0.7" top="1.15625" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>